--- a/reports/article_metrics/article_metrics.xlsx
+++ b/reports/article_metrics/article_metrics.xlsx
@@ -1209,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1220,30 +1220,716 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>expected_file</t>
+          <t>model</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>dataset_mode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>corruption</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>AP50-95</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>AP50</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>AP75</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>AR100</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>delta_AP50-95</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>delta_AP50</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>delta_AP75</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>delta_AR100</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>YOLOv8s</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>non_tiled</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>clean</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.310852</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.548504</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.326288</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>/mnt/c/Users/agd01/Documents/1ДипломМага/Проги/shelfvision/reports/article_eval/article1_tiling_robustness.csv</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Опциональный файл не найден. Создай его, если хочешь закрыть все таблицы статей без ручной склейки.</t>
-        </is>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>YOLOv8s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>non_tiled</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>blur</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.307874</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.547252</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.358595</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>/mnt/c/Users/agd01/Documents/1ДипломМага/Проги/shelfvision/reports/article_eval/article1_tiling_robustness.csv</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.002978</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.001252</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.002038</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.003955</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>YOLOv8s</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>non_tiled</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.302965</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.53868</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.314618</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.352872</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>/mnt/c/Users/agd01/Documents/1ДипломМага/Проги/shelfvision/reports/article_eval/article1_tiling_robustness.csv</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.007887</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.009823999999999999</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.01167</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.009677</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YOLOv8s</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>non_tiled</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dark</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.307608</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.536708</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.322411</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.358418</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>/mnt/c/Users/agd01/Documents/1ДипломМага/Проги/shelfvision/reports/article_eval/article1_tiling_robustness.csv</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.003244</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.011796</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.003876</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.004132</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>YOLOv8s</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>non_tiled</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>jpeg</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.308737</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.540071</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.322548</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.359633</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>/mnt/c/Users/agd01/Documents/1ДипломМага/Проги/shelfvision/reports/article_eval/article1_tiling_robustness.csv</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.002114</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.008433</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.00374</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002916</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>YOLOv8s</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>non_tiled</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>downscale</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.314362</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.549941</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.334506</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.365091</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>/mnt/c/Users/agd01/Documents/1ДипломМага/Проги/shelfvision/reports/article_eval/article1_tiling_robustness.csv</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.00351</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.001437</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.008218</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.002541</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>YOLOv8s</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>tiled</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>clean</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.538129</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.888304</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.59477</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.634481</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>/mnt/c/Users/agd01/Documents/1ДипломМага/Проги/shelfvision/reports/article_eval/article1_tiling_robustness.csv</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>YOLOv8s</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>tiled</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>blur</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.525766</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.872692</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.573089</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.62551</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>/mnt/c/Users/agd01/Documents/1ДипломМага/Проги/shelfvision/reports/article_eval/article1_tiling_robustness.csv</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.012363</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.015612</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.021681</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.008971</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>YOLOv8s</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>tiled</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.530958</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.874181</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.585716</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.626194</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>/mnt/c/Users/agd01/Documents/1ДипломМага/Проги/shelfvision/reports/article_eval/article1_tiling_robustness.csv</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.007172</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.014123</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.009054</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.008286</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>YOLOv8s</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>tiled</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>dark</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.536363</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.887635</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.589728</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.632649</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>/mnt/c/Users/agd01/Documents/1ДипломМага/Проги/shelfvision/reports/article_eval/article1_tiling_robustness.csv</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001766</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.000669</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.005042</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001832</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>YOLOv8s</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>tiled</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jpeg</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.538365</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.887412</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.594905</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.634448</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>/mnt/c/Users/agd01/Documents/1ДипломМага/Проги/shelfvision/reports/article_eval/article1_tiling_robustness.csv</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.000236</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.000892</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.000135</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.3e-05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>YOLOv8s</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>tiled</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>downscale</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.537068</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.887844</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.593734</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.633885</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>/mnt/c/Users/agd01/Documents/1ДипломМага/Проги/shelfvision/reports/article_eval/article1_tiling_robustness.csv</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.001062</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.000459</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.001036</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.000596</v>
       </c>
     </row>
   </sheetData>
@@ -2308,7 +2994,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
